--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>31812</v>
+        <v>36000</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>222684</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2 kümes x 1.060,42 m² iç alan = 2.120,84 m²; 15 adet/m² yoğunluk (rehberin 13-17 adet/m² aralığındadır).</t>
+          <t>2 kümes x 1.060,42 m² iç alan = 2.120,84 m²; 16.97 adet/m² yoğunluk (rehberin 13-17 adet/m² aralığındadır).</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>539.000 kg</t>
+          <t>610.000 kg</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -759,7 +759,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>31.812 adet/dönem x 7 dönem x %96 yaşama gücü x 2,52 kg kesim ağırlığı.</t>
+          <t>36.000 adet/dönem x 7 dönem x %96 yaşama gücü x 2,52 kg kesim ağırlığı.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 15 adet/m² yoğunluk. Yemleme 3 hat, sulama 4 hat; tünel fan debisi 2,50 m/sn hava hızına, ped alanı ve klape sayısı aynı debiye göre seçilmiştir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Mekanik projede hesaplanan ASGARİ ihtiyaç kümes başına 46.717 m³/h hava debisi, 22,86 m² ped ve 30 klapedir; kurulacak sistem 4 x 40.000 m³/h fan, 45 m² ped ve 40 klape ile bu asgari ihtiyacın üzerindedir. Yerleşim planı kurulacak bu adetlerle çizilecektir.</t>
+          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 15 adet/m² yoğunluk. Yemleme 3 hat, sulama 4 hat; tünel fan debisi 2,50 m/sn hava hızına, ped alanı ve klape sayısı aynı debiye göre seçilmiştir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Adetler mekanik projeden gelir: kümes başına 46.717 m³/h hava debisi için 4 tünel fanı ve 30 klape (30 x 1.750 = 52.500 m³/h). Yerleşim planı bu adetlerle çizilecektir.</t>
         </is>
       </c>
     </row>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="G8" s="10" t="n"/>
     </row>
-    <row r="9" ht="33" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Klape sistemi — 40 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h, 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>Klape sistemi — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -708,10 +708,10 @@
         <v>36000</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>252000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
@@ -750,7 +750,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>610.000 kg</t>
+          <t>523.000 kg</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -759,7 +759,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>36.000 adet/dönem x 7 dönem x %96 yaşama gücü x 2,52 kg kesim ağırlığı.</t>
+          <t>36.000 adet/dönem x 6 dönem x %96 yaşama gücü x 2,52 kg kesim ağırlığı.</t>
         </is>
       </c>
     </row>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -717,7 +717,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2 kümes x 1.060,42 m² iç alan = 2.120,84 m²; 16.97 adet/m² yoğunluk (rehberin 13-17 adet/m² aralığındadır).</t>
+          <t>2 kümes x 1.060,42 m² iç alan = 2.120,84 m²; 16,97 adet/m² yoğunluk (rehberin 13-17 adet/m² aralığındadır).</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 15 adet/m² yoğunluk. Yemleme 3 hat, sulama 4 hat; tünel fan debisi 2,50 m/sn hava hızına, ped alanı ve klape sayısı aynı debiye göre seçilmiştir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Adetler mekanik projeden gelir: kümes başına 46.717 m³/h hava debisi için 4 tünel fanı ve 30 klape (30 x 1.750 = 52.500 m³/h). Yerleşim planı bu adetlerle çizilecektir.</t>
+          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 16,97 adet/m² yoğunluk ile kümes başına 18.000 adet/dönem. Yemleme 3 hat, sulama 4 hat; tünel fan debisi 2,50 m/sn hava hızına, ped alanı ve klape sayısı aynı debiye göre seçilmiştir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Adetler mekanik projeden gelir: kümes başına 46.717 m³/h hava debisi için 4 tünel fanı ve 30 klape (30 x 1.750 = 52.500 m³/h). Yerleşim planı bu adetlerle çizilecektir.</t>
         </is>
       </c>
     </row>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>66 ton</t>
+          <t>57 ton</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>60 ton</t>
+          <t>51 ton</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı, 6 m³; kazı ve grobeton oturma yatağı üzerine yerleştirilir (çukur dış ölçüsü 2,00 x 2,00 m).</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Sızdırmaz betonarme foseptik; personel kullanım suyu içindir.</t>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı (6 m³); personel kullanım suyu içindir.</t>
         </is>
       </c>
     </row>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -910,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Kümes kontrol panosu — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>Kümes otomasyonu ve bilgisayar sistemi — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="55" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>KANATLILARDA OTOMATİK YEMLEME VE İÇME SUYU, SULAMA, ISITMA VE HAVALANDIRMA, ENERJİ TASARRUFU VE ÇEVRESEL OTOMATİK KONTROL SÜREÇLERİ (BÜTÇE KALEMİ 2)</t>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Yemleme sistemi — 3 hat, 243 m hat uzunluğu, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Otomatik spiral yemlik sistemi (depo motor grubu ve kaldırma dâhil) — 3 hat, 243 m yemlik hattı, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1035,11 +1035,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Sulama sistemi — 4 hat, hat başına 312 m, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Otomatik nipel suluk sistemi (regülatör, hat sonu ve kaldırma dâhil) — Kümes başına 4 hat, toplam 312 m hat, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 4 hat sonu, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="G6" s="10" t="n"/>
     </row>
-    <row r="7" ht="33" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tünel havalandırma fanı — 4 adet, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
+          <t>Havalandırma fanları — Kümes başına 4 adet tünel fanı, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1081,11 +1081,11 @@
       </c>
       <c r="G7" s="10" t="n"/>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Soğutma pedi sistemi — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, 2 x 15 m uzunluk (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1104,11 +1104,11 @@
       </c>
       <c r="G8" s="10" t="n"/>
     </row>
-    <row r="9" ht="55" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Klape sistemi — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>Hava klape sistemi (açma-kapama hattı dâhil) — Kümes başına 30 adet 26 x 56 cm izolasyonlu plastik klape, 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1131,7 +1131,7 @@
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Yem silosu ve nakil sistemi — En az 17,77 ton galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+          <t>17,67 ton silo ve aktarma grubu — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1151,15 +1151,15 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="11" t="n"/>
+      <c r="A11" s="10" t="n"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Kümes ısıtma sistemi — katı yakıtlı merkezi sistem sıcak hava üreteci, kümes başına en az 290 kW (249.000 kcal/h)</t>
+          <t>Aydınlatma sistemi — Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HZC-LGHT-01</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
@@ -1171,41 +1171,35 @@
       <c r="F11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>KANATLILARDA BİYOGÜVENLİĞİN SAĞLANMASI</t>
-        </is>
-      </c>
+      <c r="G11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="11" t="n"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Isıtma sistemi — 350.000 kcal/h — Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HZC-HEA-004</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Kümes girişinde hijyen bariyeri ve dezenfeksiyon havuzu yapı işleri kapsamındadır; parsel çevresi tel çit ile kapatılmıştır.</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="11" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>KANATLILARDA GÜBRE VE ATIK YÖNETİMİ, İŞLEME VE DEPOLAMA SÜRECİ</t>
+          <t>KANATLILARDA BİYOGÜVENLİĞİN SAĞLANMASI</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1227,14 +1221,14 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Sızdırmaz betonarme gübre çukuru ve ölü atma çukuru yapı işleri kapsamındadır; kapasiteleri rehberin 0,28 m³/hafta/1000 hayvan ve 3 x 3 x 3 m ölçütlerine göre boyutlandırılmıştır.</t>
+          <t>Kümes girişinde hijyen bariyeri ve dezenfeksiyon havuzu yapı işleri kapsamındadır; parsel çevresi tel çit ile kapatılmıştır.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>KANATLILARDA HAYVAN SAĞLIĞI VE BAKIM SÜRECİ (TARTMA, DEZENFEKSİYON, GAGA KESİMİ, AŞILAMA VB.)</t>
+          <t>KANATLILARDA GÜBRE VE ATIK YÖNETİMİ, İŞLEME VE DEPOLAMA SÜRECİ</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1256,30 +1250,59 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>Sızdırmaz betonarme gübre çukuru ve ölü atma çukuru yapı işleri kapsamındadır; kapasiteleri rehberin 0,28 m³/hafta/1000 hayvan ve 3 x 3 x 3 m ölçütlerine göre boyutlandırılmıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>KANATLILARDA HAYVAN SAĞLIĞI VE BAKIM SÜRECİ (TARTMA, DEZENFEKSİYON, GAGA KESİMİ, AŞILAMA VB.)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>Aşılama ve veteriner hizmetleri sözleşmeli üretim kapsamında entegratör tarafından yürütülür; işletmede ayrı ekipman öngörülmemiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Sayfa No:</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
+          <t>Sayfa No:</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
           <t>Paraf:</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="G5:G11"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A5:A12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A5:A11"/>
+    <mergeCell ref="G5:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 16,97 adet/m² yoğunluk ile kümes başına 18.000 adet/dönem. Yemleme 3 hat, sulama 4 hat; tünel fan debisi 2,50 m/sn hava hızına, ped alanı ve klape sayısı aynı debiye göre seçilmiştir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Adetler mekanik projeden gelir: kümes başına 46.717 m³/h hava debisi için 4 tünel fanı ve 30 klape (30 x 1.750 = 52.500 m³/h). Yerleşim planı bu adetlerle çizilecektir.</t>
+          <t>Kapasiteler kümesin kendi ölçüsünden çıkar: 78,55 x 13,50 m iç alan, 16,97 adet/m² yoğunluk ile kümes başına 18.000 adet/dönem. Yemleme 3 hat, sulama 4 hat (toplam 312 m). ADETLER ONAYLI HAVALANDIRMA PROJESİNDEN GELİR: asgari hava debisi 46.717 m³/h olup 30 klape ile karşılanır (30 x 1.750 = 52.500 m³/h); tünel havalandırmada 4 fan bulunur ve 4 x 40.000 = 160.000 m³/h verir, bu da 48,46 m² kesitte yaklaşık 0,92 m/sn kesit hızına karşılık gelir. Soğutma pedi alanı 45 m²'dir. Isıtma kapasitesi kümesin ısı yükü hesabından gelir. Yerleşim planı bu adetlerle çizilmiştir.</t>
         </is>
       </c>
     </row>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -3236,7 +3236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="35.71" customWidth="1" style="99" min="1" max="1"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D6" s="69" t="inlineStr">
         <is>
-          <t>HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>HZC-70 işlemcili pano; 5 ısı, 1 nem, 1 basınç sensörü, ek alarm sensörü, sensör kablolamaları, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
         </is>
       </c>
       <c r="E6" s="69" t="inlineStr">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="F6" s="69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="69" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       <c r="A19" s="140" t="n"/>
       <c r="B19" s="73" t="inlineStr">
         <is>
-          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil)</t>
+          <t>Soğutma petekleri ve kapatma sistemi</t>
         </is>
       </c>
       <c r="C19" s="73" t="inlineStr">
@@ -3840,7 +3840,7 @@
       <c r="A21" s="140" t="n"/>
       <c r="B21" s="73" t="inlineStr">
         <is>
-          <t>17,67 ton silo ve aktarma grubu</t>
+          <t>Silo ve aktarma sistemi — 17,67 ton</t>
         </is>
       </c>
       <c r="C21" s="73" t="inlineStr">
@@ -3881,10 +3881,10 @@
       <c r="L21" s="140" t="n"/>
     </row>
     <row r="22" ht="12.75" customHeight="1" s="99">
-      <c r="A22" s="140" t="n"/>
+      <c r="A22" s="141" t="n"/>
       <c r="B22" s="73" t="inlineStr">
         <is>
-          <t>Aydınlatma sistemi</t>
+          <t>Isıtma sistemi — 350.000 kcal/h</t>
         </is>
       </c>
       <c r="C22" s="73" t="inlineStr">
@@ -3892,9 +3892,9 @@
           <t>— (marka bağımsız şartname; yeni alınacak)</t>
         </is>
       </c>
-      <c r="D22" s="73" t="inlineStr">
-        <is>
-          <t>Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
+      <c r="D22" s="69" t="inlineStr">
+        <is>
+          <t>Kümes başına 1 adet katı yakıtlı ısıtma kazanı, brandalı model, 171 m hava kanalı; en az 1.700 m² ısıtma alanı, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan</t>
         </is>
       </c>
       <c r="E22" s="73" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G22" s="73" t="inlineStr">
         <is>
-          <t>Kümes içi aydınlatma</t>
+          <t>Kümes ısıtması ve civciv dönemi ön ısıtma</t>
         </is>
       </c>
       <c r="H22" s="73" t="n"/>
@@ -3922,97 +3922,67 @@
           <t>X</t>
         </is>
       </c>
-      <c r="L22" s="140" t="n"/>
+      <c r="L22" s="141" t="n"/>
     </row>
     <row r="23" ht="12.75" customHeight="1" s="99">
-      <c r="A23" s="141" t="n"/>
+      <c r="A23" s="90" t="inlineStr">
+        <is>
+          <t>KANATLILARDA BİYOGÜVENLİĞİN SAĞLANMASI</t>
+        </is>
+      </c>
       <c r="B23" s="73" t="inlineStr">
         <is>
-          <t>Isıtma sistemi — 350.000 kcal/h</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" s="73" t="inlineStr">
         <is>
-          <t>— (marka bağımsız şartname; yeni alınacak)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="69" t="inlineStr">
         <is>
-          <t>Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="73" t="inlineStr">
         <is>
-          <t>2 set</t>
-        </is>
-      </c>
-      <c r="F23" s="73" t="n">
-        <v>8</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G23" s="73" t="inlineStr">
         <is>
-          <t>Kümes ısıtması ve civciv dönemi ön ısıtma</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="73" t="n"/>
-      <c r="I23" s="73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="I23" s="73" t="n"/>
       <c r="J23" s="73" t="n"/>
-      <c r="K23" s="73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L23" s="141" t="n"/>
+      <c r="K23" s="73" t="n"/>
+      <c r="L23" s="75" t="inlineStr">
+        <is>
+          <t>Kümes girişinde hijyen bariyeri ve dezenfeksiyon havuzu yapı işleri kapsamındadır; parsel çevresi tel çit ile kapatılmıştır.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="12.75" customHeight="1" s="99">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>KANATLILARDA BİYOGÜVENLİĞİN SAĞLANMASI</t>
-        </is>
-      </c>
-      <c r="B24" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A24" s="140" t="n"/>
+      <c r="B24" s="73" t="n"/>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="69" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="73" t="n"/>
+      <c r="G24" s="73" t="n"/>
       <c r="H24" s="73" t="n"/>
       <c r="I24" s="73" t="n"/>
       <c r="J24" s="73" t="n"/>
       <c r="K24" s="73" t="n"/>
-      <c r="L24" s="75" t="inlineStr">
-        <is>
-          <t>Kümes girişinde hijyen bariyeri ve dezenfeksiyon havuzu yapı işleri kapsamındadır; parsel çevresi tel çit ile kapatılmıştır.</t>
-        </is>
-      </c>
+      <c r="L24" s="75" t="n"/>
     </row>
     <row r="25" ht="12.75" customHeight="1" s="99">
       <c r="A25" s="140" t="n"/>
@@ -4043,10 +4013,10 @@
       <c r="L26" s="75" t="n"/>
     </row>
     <row r="27" ht="12.75" customHeight="1" s="99">
-      <c r="A27" s="140" t="n"/>
+      <c r="A27" s="141" t="n"/>
       <c r="B27" s="73" t="n"/>
       <c r="C27" s="73" t="n"/>
-      <c r="D27" s="69" t="n"/>
+      <c r="D27" s="73" t="n"/>
       <c r="E27" s="73" t="n"/>
       <c r="F27" s="73" t="n"/>
       <c r="G27" s="73" t="n"/>
@@ -4054,67 +4024,67 @@
       <c r="I27" s="73" t="n"/>
       <c r="J27" s="73" t="n"/>
       <c r="K27" s="73" t="n"/>
-      <c r="L27" s="75" t="n"/>
+      <c r="L27" s="73" t="n"/>
     </row>
     <row r="28" ht="12.75" customHeight="1" s="99">
-      <c r="A28" s="141" t="n"/>
-      <c r="B28" s="73" t="n"/>
-      <c r="C28" s="73" t="n"/>
-      <c r="D28" s="73" t="n"/>
-      <c r="E28" s="73" t="n"/>
-      <c r="F28" s="73" t="n"/>
-      <c r="G28" s="73" t="n"/>
+      <c r="A28" s="90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANATLILARDA GÜBRE VE ATIK YÖNETİMİ, İŞLEME VE DEPOLAMA SÜRECİ </t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H28" s="73" t="n"/>
       <c r="I28" s="73" t="n"/>
       <c r="J28" s="73" t="n"/>
       <c r="K28" s="73" t="n"/>
-      <c r="L28" s="73" t="n"/>
+      <c r="L28" s="73" t="inlineStr">
+        <is>
+          <t>Sızdırmaz betonarme gübre çukuru ve ölü atma çukuru yapı işleri kapsamındadır; kapasiteleri rehberin 0,28 m³/hafta/1000 hayvan ve 3 x 3 x 3 m ölçütlerine göre boyutlandırılmıştır.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="12.75" customHeight="1" s="99">
-      <c r="A29" s="90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KANATLILARDA GÜBRE VE ATIK YÖNETİMİ, İŞLEME VE DEPOLAMA SÜRECİ </t>
-        </is>
-      </c>
-      <c r="B29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A29" s="140" t="n"/>
+      <c r="B29" s="73" t="n"/>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="73" t="n"/>
+      <c r="G29" s="73" t="n"/>
       <c r="H29" s="73" t="n"/>
       <c r="I29" s="73" t="n"/>
       <c r="J29" s="73" t="n"/>
       <c r="K29" s="73" t="n"/>
-      <c r="L29" s="73" t="inlineStr">
-        <is>
-          <t>Sızdırmaz betonarme gübre çukuru ve ölü atma çukuru yapı işleri kapsamındadır; kapasiteleri rehberin 0,28 m³/hafta/1000 hayvan ve 3 x 3 x 3 m ölçütlerine göre boyutlandırılmıştır.</t>
-        </is>
-      </c>
+      <c r="L29" s="73" t="n"/>
     </row>
     <row r="30" ht="12.75" customHeight="1" s="99">
       <c r="A30" s="140" t="n"/>
@@ -4145,7 +4115,7 @@
       <c r="L31" s="73" t="n"/>
     </row>
     <row r="32" ht="12.75" customHeight="1" s="99">
-      <c r="A32" s="140" t="n"/>
+      <c r="A32" s="141" t="n"/>
       <c r="B32" s="73" t="n"/>
       <c r="C32" s="73" t="n"/>
       <c r="D32" s="73" t="n"/>
@@ -4159,64 +4129,64 @@
       <c r="L32" s="73" t="n"/>
     </row>
     <row r="33" ht="12.75" customHeight="1" s="99">
-      <c r="A33" s="141" t="n"/>
-      <c r="B33" s="73" t="n"/>
-      <c r="C33" s="73" t="n"/>
-      <c r="D33" s="73" t="n"/>
-      <c r="E33" s="73" t="n"/>
-      <c r="F33" s="73" t="n"/>
-      <c r="G33" s="73" t="n"/>
+      <c r="A33" s="90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANATLILARDA HAYVAN SAĞLIĞI VE BAKIM SÜRECİ (TARTMA, DEZENFEKSİYON, GAGAKESİMİ, AŞILAMA VB.) </t>
+        </is>
+      </c>
+      <c r="B33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H33" s="73" t="n"/>
       <c r="I33" s="73" t="n"/>
       <c r="J33" s="73" t="n"/>
       <c r="K33" s="73" t="n"/>
-      <c r="L33" s="73" t="n"/>
+      <c r="L33" s="73" t="inlineStr">
+        <is>
+          <t>Aşılama ve veteriner hizmetleri sözleşmeli üretim kapsamında entegratör tarafından yürütülür; işletmede ayrı ekipman öngörülmemiştir.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="12.75" customHeight="1" s="99">
-      <c r="A34" s="90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KANATLILARDA HAYVAN SAĞLIĞI VE BAKIM SÜRECİ (TARTMA, DEZENFEKSİYON, GAGAKESİMİ, AŞILAMA VB.) </t>
-        </is>
-      </c>
-      <c r="B34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A34" s="140" t="n"/>
+      <c r="B34" s="73" t="n"/>
+      <c r="C34" s="73" t="n"/>
+      <c r="D34" s="73" t="n"/>
+      <c r="E34" s="73" t="n"/>
+      <c r="F34" s="73" t="n"/>
+      <c r="G34" s="73" t="n"/>
       <c r="H34" s="73" t="n"/>
       <c r="I34" s="73" t="n"/>
       <c r="J34" s="73" t="n"/>
       <c r="K34" s="73" t="n"/>
-      <c r="L34" s="73" t="inlineStr">
-        <is>
-          <t>Aşılama ve veteriner hizmetleri sözleşmeli üretim kapsamında entegratör tarafından yürütülür; işletmede ayrı ekipman öngörülmemiştir.</t>
-        </is>
-      </c>
+      <c r="L34" s="73" t="n"/>
     </row>
     <row r="35" ht="12.75" customHeight="1" s="99">
       <c r="A35" s="140" t="n"/>
@@ -4247,7 +4217,7 @@
       <c r="L36" s="73" t="n"/>
     </row>
     <row r="37" ht="12.75" customHeight="1" s="99">
-      <c r="A37" s="140" t="n"/>
+      <c r="A37" s="141" t="n"/>
       <c r="B37" s="73" t="n"/>
       <c r="C37" s="73" t="n"/>
       <c r="D37" s="73" t="n"/>
@@ -4261,65 +4231,65 @@
       <c r="L37" s="73" t="n"/>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="99">
-      <c r="A38" s="141" t="n"/>
-      <c r="B38" s="73" t="n"/>
-      <c r="C38" s="73" t="n"/>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="73" t="n"/>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="73" t="n"/>
+      <c r="A38" s="90" t="inlineStr">
+        <is>
+          <t>YUKARIDA DEĞİNİLMEYEN DİĞER SÜREÇLER
+(……………………………….. SÜRECİ)</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="H38" s="73" t="n"/>
       <c r="I38" s="73" t="n"/>
       <c r="J38" s="73" t="n"/>
       <c r="K38" s="73" t="n"/>
-      <c r="L38" s="73" t="n"/>
+      <c r="L38" s="73" t="inlineStr">
+        <is>
+          <t>Yukarıda değinilmeyen ayrı bir süreç ve ona ait makine-ekipman bulunmamaktadır.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="99">
-      <c r="A39" s="90" t="inlineStr">
-        <is>
-          <t>YUKARIDA DEĞİNİLMEYEN DİĞER SÜREÇLER
-(……………………………….. SÜRECİ)</t>
-        </is>
-      </c>
-      <c r="B39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A39" s="140" t="n"/>
+      <c r="B39" s="73" t="n"/>
+      <c r="C39" s="73" t="n"/>
+      <c r="D39" s="73" t="n"/>
+      <c r="E39" s="73" t="n"/>
+      <c r="F39" s="73" t="n"/>
+      <c r="G39" s="73" t="n"/>
       <c r="H39" s="73" t="n"/>
       <c r="I39" s="73" t="n"/>
       <c r="J39" s="73" t="n"/>
       <c r="K39" s="73" t="n"/>
-      <c r="L39" s="73" t="inlineStr">
-        <is>
-          <t>Yukarıda değinilmeyen ayrı bir süreç ve ona ait makine-ekipman bulunmamaktadır.</t>
-        </is>
-      </c>
+      <c r="L39" s="73" t="n"/>
     </row>
     <row r="40" ht="12.75" customHeight="1" s="99">
       <c r="A40" s="140" t="n"/>
@@ -4350,7 +4320,7 @@
       <c r="L41" s="73" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1" s="99">
-      <c r="A42" s="140" t="n"/>
+      <c r="A42" s="141" t="n"/>
       <c r="B42" s="73" t="n"/>
       <c r="C42" s="73" t="n"/>
       <c r="D42" s="73" t="n"/>
@@ -4364,21 +4334,25 @@
       <c r="L42" s="73" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1" s="99">
-      <c r="A43" s="141" t="n"/>
-      <c r="B43" s="73" t="n"/>
-      <c r="C43" s="73" t="n"/>
-      <c r="D43" s="73" t="n"/>
-      <c r="E43" s="73" t="n"/>
-      <c r="F43" s="73" t="n"/>
-      <c r="G43" s="73" t="n"/>
-      <c r="H43" s="73" t="n"/>
-      <c r="I43" s="73" t="n"/>
-      <c r="J43" s="73" t="n"/>
-      <c r="K43" s="73" t="n"/>
-      <c r="L43" s="73" t="n"/>
+      <c r="A43" s="142" t="n"/>
+      <c r="B43" s="78" t="n"/>
+      <c r="C43" s="78" t="n"/>
+      <c r="D43" s="78" t="n"/>
+      <c r="E43" s="78" t="n"/>
+      <c r="F43" s="78" t="n"/>
+      <c r="G43" s="78" t="n"/>
+      <c r="H43" s="78" t="n"/>
+      <c r="I43" s="47" t="inlineStr">
+        <is>
+          <t>Sayfa No:</t>
+        </is>
+      </c>
+      <c r="J43" s="78" t="n"/>
+      <c r="K43" s="78" t="n"/>
+      <c r="L43" s="78" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1" s="99">
-      <c r="A44" s="142" t="n"/>
+      <c r="A44" s="140" t="n"/>
       <c r="B44" s="78" t="n"/>
       <c r="C44" s="78" t="n"/>
       <c r="D44" s="78" t="n"/>
@@ -4388,7 +4362,7 @@
       <c r="H44" s="78" t="n"/>
       <c r="I44" s="47" t="inlineStr">
         <is>
-          <t>Sayfa No:</t>
+          <t>Paraf:</t>
         </is>
       </c>
       <c r="J44" s="78" t="n"/>
@@ -4396,7 +4370,7 @@
       <c r="L44" s="78" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1" s="99">
-      <c r="A45" s="140" t="n"/>
+      <c r="A45" s="78" t="n"/>
       <c r="B45" s="78" t="n"/>
       <c r="C45" s="78" t="n"/>
       <c r="D45" s="78" t="n"/>
@@ -4404,11 +4378,7 @@
       <c r="F45" s="78" t="n"/>
       <c r="G45" s="78" t="n"/>
       <c r="H45" s="78" t="n"/>
-      <c r="I45" s="47" t="inlineStr">
-        <is>
-          <t>Paraf:</t>
-        </is>
-      </c>
+      <c r="I45" s="78" t="n"/>
       <c r="J45" s="78" t="n"/>
       <c r="K45" s="78" t="n"/>
       <c r="L45" s="78" t="n"/>
@@ -5211,42 +5181,28 @@
       <c r="K102" s="78" t="n"/>
       <c r="L102" s="78" t="n"/>
     </row>
-    <row r="103">
-      <c r="A103" s="78" t="n"/>
-      <c r="B103" s="78" t="n"/>
-      <c r="C103" s="78" t="n"/>
-      <c r="D103" s="78" t="n"/>
-      <c r="E103" s="78" t="n"/>
-      <c r="F103" s="78" t="n"/>
-      <c r="G103" s="78" t="n"/>
-      <c r="H103" s="78" t="n"/>
-      <c r="I103" s="78" t="n"/>
-      <c r="J103" s="78" t="n"/>
-      <c r="K103" s="78" t="n"/>
-      <c r="L103" s="78" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A16:A22"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="B3:L3"/>
+    <mergeCell ref="A33:A37"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A23:A27"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A29:A33"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="L16:L23"/>
+    <mergeCell ref="A38:A42"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="A28:A32"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A16:A23"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A24:A28"/>
     <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A43:A44"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
+    <mergeCell ref="L16:L22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A3:A5"/>
   </mergeCells>

--- a/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
+++ b/belgeler/44_TEKNIK_PROJE_TP1013.xlsx
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C9" s="69" t="inlineStr">
         <is>
-          <t>2 adet, her biri 2,90 x 2,90 m. Yem silolarının betonarme kaideleri.</t>
+          <t>2 adet; her biri 2,90 x 2,90 m radye temel (H = 0,40 m, kot -0,10 / +0,30) ve üzerinde 4 adet SB01…SB04 kolonu (40/40, kot +0,30 / +1,40). Yem silolarının betonarme kaideleri.</t>
         </is>
       </c>
       <c r="D9" s="148" t="n">
